--- a/crianza.xlsx
+++ b/crianza.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pirata\pkReloaded\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pepe\Documents\Jueguitos\pkReloaded\data\partidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99673816-2E87-4521-BF01-F69167454045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E9241A-079B-48C3-A029-8F572F6916BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="9030" windowWidth="12195" windowHeight="6960" xr2:uid="{7ACB3B34-B20F-450C-9413-C21BAFBDEBDD}"/>
+    <workbookView xWindow="720" yWindow="8220" windowWidth="12585" windowHeight="6180" xr2:uid="{7ACB3B34-B20F-450C-9413-C21BAFBDEBDD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -443,9 +443,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -483,7 +483,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -589,7 +589,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -731,7 +731,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -800,13 +800,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="16">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -823,7 +823,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="6">
@@ -844,11 +844,11 @@
         <v>10</v>
       </c>
       <c r="D6" s="6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="1"/>
@@ -865,11 +865,11 @@
         <v>10</v>
       </c>
       <c r="D7" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="1"/>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="1">
@@ -911,7 +911,7 @@
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="13"/>

--- a/crianza.xlsx
+++ b/crianza.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pepe\Documents\Jueguitos\pkReloaded\data\partidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E9241A-079B-48C3-A029-8F572F6916BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A8541B-6051-41AA-9F20-50C32D79C77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="8220" windowWidth="12585" windowHeight="6180" xr2:uid="{7ACB3B34-B20F-450C-9413-C21BAFBDEBDD}"/>
   </bookViews>
@@ -800,13 +800,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" s="16">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -844,11 +844,11 @@
         <v>10</v>
       </c>
       <c r="D6" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="1"/>
@@ -865,11 +865,11 @@
         <v>10</v>
       </c>
       <c r="D7" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="1"/>
@@ -907,11 +907,11 @@
         <v>10</v>
       </c>
       <c r="D9" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="13"/>
